--- a/xlsx/cards-pages/cards.snh48.xlsx
+++ b/xlsx/cards-pages/cards.snh48.xlsx
@@ -197,7 +197,7 @@
     <t>芦馨怡</t>
   </si>
   <si>
-    <t>https://bkimg.cdn.bcebos.com/pic/aa18972bd40735fae6cd8d304d0618b30f2443a7a2b8?x-bce-process=image/format,f_auto/quality,Q_70/resize,m_lfit,limit_1,w_536</t>
+    <t>https://zhengxie.info/topics/snh48/assets/images/芦馨怡.webp</t>
   </si>
   <si>
     <t>SNH48 官方主页 - 芦馨怡</t>
@@ -1011,7 +1011,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1025,13 +1025,6 @@
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1474,28 +1467,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1504,124 +1500,121 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1970,6 +1963,9 @@
   <sheetPr/>
   <dimension ref="A1:AG90"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="8" max="8" width="13.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:33">
       <c r="A1" t="s">
@@ -11063,7 +11059,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H7" r:id="rId1" display="https://bkimg.cdn.bcebos.com/pic/aa18972bd40735fae6cd8d304d0618b30f2443a7a2b8?x-bce-process=image/format,f_auto/quality,Q_70/resize,m_lfit,limit_1,w_536"/>
+    <hyperlink ref="H7" r:id="rId1" display="https://zhengxie.info/topics/snh48/assets/images/芦馨怡.webp" tooltip="https://zhengxie.info/topics/snh48/assets/images/芦馨怡.webp"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/xlsx/cards-pages/cards.snh48.xlsx
+++ b/xlsx/cards-pages/cards.snh48.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25515" windowHeight="8010"/>
+    <workbookView windowWidth="25515" windowHeight="7410"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2792" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2792" uniqueCount="329">
   <si>
     <t>row_seq</t>
   </si>
@@ -831,6 +831,9 @@
   </si>
   <si>
     <t>钟郭菲杨</t>
+  </si>
+  <si>
+    <t>钟郭菲杨,#9E1B22</t>
   </si>
   <si>
     <t>SNH48 官方主页 - 钟郭菲杨</t>
@@ -9173,7 +9176,7 @@
         <v>227</v>
       </c>
       <c r="H72" t="s">
-        <v>40</v>
+        <v>268</v>
       </c>
       <c r="I72" t="s">
         <v>228</v>
@@ -9185,10 +9188,10 @@
         <v>40</v>
       </c>
       <c r="L72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N72" t="s">
         <v>40</v>
@@ -9268,7 +9271,7 @@
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G73" t="s">
         <v>227</v>
@@ -9286,10 +9289,10 @@
         <v>40</v>
       </c>
       <c r="L73" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M73" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N73" t="s">
         <v>40</v>
@@ -9369,7 +9372,7 @@
         <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G74" t="s">
         <v>227</v>
@@ -9387,10 +9390,10 @@
         <v>40</v>
       </c>
       <c r="L74" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M74" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N74" t="s">
         <v>40</v>
@@ -9470,7 +9473,7 @@
         <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G75" t="s">
         <v>227</v>
@@ -9488,10 +9491,10 @@
         <v>40</v>
       </c>
       <c r="L75" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M75" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N75" t="s">
         <v>40</v>
@@ -9562,25 +9565,25 @@
         <v>33</v>
       </c>
       <c r="C76" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D76" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E76">
         <v>1</v>
       </c>
       <c r="F76" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G76" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H76" t="s">
         <v>40</v>
       </c>
       <c r="I76" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J76" t="s">
         <v>40</v>
@@ -9589,10 +9592,10 @@
         <v>40</v>
       </c>
       <c r="L76" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M76" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N76" t="s">
         <v>40</v>
@@ -9663,25 +9666,25 @@
         <v>33</v>
       </c>
       <c r="C77" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D77" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G77" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H77" t="s">
         <v>40</v>
       </c>
       <c r="I77" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J77" t="s">
         <v>40</v>
@@ -9690,10 +9693,10 @@
         <v>40</v>
       </c>
       <c r="L77" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M77" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N77" t="s">
         <v>40</v>
@@ -9764,25 +9767,25 @@
         <v>33</v>
       </c>
       <c r="C78" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D78" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E78">
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G78" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H78" t="s">
         <v>40</v>
       </c>
       <c r="I78" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J78" t="s">
         <v>40</v>
@@ -9791,10 +9794,10 @@
         <v>40</v>
       </c>
       <c r="L78" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M78" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N78" t="s">
         <v>40</v>
@@ -9865,25 +9868,25 @@
         <v>33</v>
       </c>
       <c r="C79" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D79" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G79" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H79" t="s">
         <v>40</v>
       </c>
       <c r="I79" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J79" t="s">
         <v>40</v>
@@ -9892,10 +9895,10 @@
         <v>40</v>
       </c>
       <c r="L79" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M79" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N79" t="s">
         <v>40</v>
@@ -9966,25 +9969,25 @@
         <v>33</v>
       </c>
       <c r="C80" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D80" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E80">
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G80" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H80" t="s">
         <v>40</v>
       </c>
       <c r="I80" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J80" t="s">
         <v>40</v>
@@ -9993,10 +9996,10 @@
         <v>40</v>
       </c>
       <c r="L80" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M80" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N80" t="s">
         <v>40</v>
@@ -10067,25 +10070,25 @@
         <v>33</v>
       </c>
       <c r="C81" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D81" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E81">
         <v>1</v>
       </c>
       <c r="F81" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H81" t="s">
         <v>40</v>
       </c>
       <c r="I81" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J81" t="s">
         <v>40</v>
@@ -10094,10 +10097,10 @@
         <v>40</v>
       </c>
       <c r="L81" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M81" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N81" t="s">
         <v>40</v>
@@ -10168,25 +10171,25 @@
         <v>33</v>
       </c>
       <c r="C82" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D82" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E82">
         <v>1</v>
       </c>
       <c r="F82" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G82" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H82" t="s">
         <v>40</v>
       </c>
       <c r="I82" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J82" t="s">
         <v>40</v>
@@ -10195,10 +10198,10 @@
         <v>40</v>
       </c>
       <c r="L82" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="M82" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="N82" t="s">
         <v>40</v>
@@ -10269,25 +10272,25 @@
         <v>33</v>
       </c>
       <c r="C83" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D83" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E83">
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="G83" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H83" t="s">
         <v>40</v>
       </c>
       <c r="I83" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J83" t="s">
         <v>40</v>
@@ -10296,10 +10299,10 @@
         <v>40</v>
       </c>
       <c r="L83" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M83" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N83" t="s">
         <v>40</v>
@@ -10370,25 +10373,25 @@
         <v>33</v>
       </c>
       <c r="C84" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D84" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E84">
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G84" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H84" t="s">
         <v>40</v>
       </c>
       <c r="I84" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J84" t="s">
         <v>40</v>
@@ -10397,10 +10400,10 @@
         <v>40</v>
       </c>
       <c r="L84" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M84" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N84" t="s">
         <v>40</v>
@@ -10471,25 +10474,25 @@
         <v>33</v>
       </c>
       <c r="C85" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D85" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E85">
         <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G85" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H85" t="s">
         <v>40</v>
       </c>
       <c r="I85" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J85" t="s">
         <v>40</v>
@@ -10498,10 +10501,10 @@
         <v>40</v>
       </c>
       <c r="L85" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M85" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N85" t="s">
         <v>40</v>
@@ -10572,25 +10575,25 @@
         <v>33</v>
       </c>
       <c r="C86" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D86" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H86" t="s">
         <v>40</v>
       </c>
       <c r="I86" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J86" t="s">
         <v>40</v>
@@ -10599,10 +10602,10 @@
         <v>40</v>
       </c>
       <c r="L86" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M86" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N86" t="s">
         <v>40</v>
@@ -10673,25 +10676,25 @@
         <v>33</v>
       </c>
       <c r="C87" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D87" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E87">
         <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G87" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H87" t="s">
         <v>40</v>
       </c>
       <c r="I87" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J87" t="s">
         <v>40</v>
@@ -10700,10 +10703,10 @@
         <v>40</v>
       </c>
       <c r="L87" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M87" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N87" t="s">
         <v>40</v>
@@ -10774,25 +10777,25 @@
         <v>33</v>
       </c>
       <c r="C88" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D88" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E88">
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="G88" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H88" t="s">
         <v>40</v>
       </c>
       <c r="I88" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J88" t="s">
         <v>40</v>
@@ -10801,10 +10804,10 @@
         <v>40</v>
       </c>
       <c r="L88" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M88" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N88" t="s">
         <v>40</v>
@@ -10875,25 +10878,25 @@
         <v>33</v>
       </c>
       <c r="C89" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D89" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E89">
         <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G89" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H89" t="s">
         <v>40</v>
       </c>
       <c r="I89" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J89" t="s">
         <v>40</v>
@@ -10902,10 +10905,10 @@
         <v>40</v>
       </c>
       <c r="L89" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M89" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N89" t="s">
         <v>40</v>
@@ -10976,25 +10979,25 @@
         <v>33</v>
       </c>
       <c r="C90" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D90" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E90">
         <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G90" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H90" t="s">
         <v>40</v>
       </c>
       <c r="I90" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J90" t="s">
         <v>40</v>
@@ -11003,10 +11006,10 @@
         <v>40</v>
       </c>
       <c r="L90" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M90" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N90" t="s">
         <v>40</v>
